--- a/config/generated/templates/NativeHandler.xlsx
+++ b/config/generated/templates/NativeHandler.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="33">
   <si>
     <t>@table</t>
   </si>
@@ -43,7 +43,7 @@
     <t>@schema</t>
   </si>
   <si>
-    <t>672e41ba07d08321</t>
+    <t>162a5f35ebf31c95</t>
   </si>
   <si>
     <t>#name</t>
@@ -55,9 +55,6 @@
     <t>domain</t>
   </si>
   <si>
-    <t>handler_version</t>
-  </si>
-  <si>
     <t>argument_schema_sha256</t>
   </si>
   <si>
@@ -104,9 +101,6 @@
   </si>
   <si>
     <t>length=1..160</t>
-  </si>
-  <si>
-    <t>length=1..80</t>
   </si>
   <si>
     <t>length=64..64</t>
@@ -535,22 +529,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="3" width="12.7109375" style="5" customWidth="1"/>
     <col min="4" max="4" width="16.7109375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" style="5" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" style="5" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" style="5" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="23.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -582,7 +575,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="24" customHeight="1">
+    <row r="2" spans="1:10" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
@@ -613,13 +606,10 @@
       <c r="J2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="4" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="4" t="s">
-        <v>20</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>5</v>
@@ -648,114 +638,102 @@
       <c r="J3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>19</v>
-      </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4" s="5" t="s">
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="B5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="4" t="s">
+    <row r="6" spans="1:10">
+      <c r="A6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>29</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="H6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" ht="42" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" s="5"/>
-    </row>
-    <row r="7" spans="1:11" ht="42" customHeight="1">
-      <c r="A7" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -766,7 +744,6 @@
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -777,7 +754,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Battle, Activity" promptTitle="RuleDomain enum" prompt="Select a value from the dropdown." sqref="D8:D1007">
       <formula1>"Battle,Activity"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="J8:J1007">
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>

--- a/config/generated/templates/NativeHandler.xlsx
+++ b/config/generated/templates/NativeHandler.xlsx
@@ -34,16 +34,16 @@
     <t>id</t>
   </si>
   <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
+    <t>@groups</t>
+  </si>
+  <si>
+    <t>common</t>
   </si>
   <si>
     <t>@schema</t>
   </si>
   <si>
-    <t>162a5f35ebf31c95</t>
+    <t>6df8aafc9c1bb3b7</t>
   </si>
   <si>
     <t>#name</t>
@@ -91,7 +91,7 @@
     <t>bool</t>
   </si>
   <si>
-    <t>#scope</t>
+    <t>#groups</t>
   </si>
   <si>
     <t>#input</t>
